--- a/public/documents/pieces-defense/RF-reconstitution-volumes-liquides.xlsx
+++ b/public/documents/pieces-defense/RF-reconstitution-volumes-liquides.xlsx
@@ -511,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -708,85 +708,154 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Sur-versement au verre (~8 %)</t>
+          <t>Sur-versement au verre et cocktails (free-pour, Kerr 2008)</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>446</v>
+        <v>807</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0.04198832611560911</v>
+        <v>0.07597439276972322</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Calcul (recettes x ventes)</t>
+          <t>Estimation bornee</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Degustation</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Stock final (inventaire)</t>
+          <t>Degustation offerte (pichet + vin nomme au verre)</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>213</v>
+        <v>113</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0.02005272076821691</v>
+        <v>0.01063829787234043</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Mesure (caisse/inventaire)</t>
+          <t>Estimation bornee</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t>Cremant jete</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Cremant jete en fin de journee (eventé)</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>126</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.01186217284880437</v>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Estimation bornee</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Freinte biere</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Freinte technique de la biere pression (mousse, lignes)</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>129</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>0.01214460553568066</v>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Estimation bornee</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Stock final (inventaire)</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>213</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.02005272076821691</v>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Mesure (caisse/inventaire)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
           <t>Perte reelle</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Perte reelle (casse, evaporation, fonds de verre, rincage)</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n">
-        <v>2419</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>0.2277348898512521</v>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>1690</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>0.1591037469403126</v>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Residu (= achats - traces)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>TOTAL ACHATS</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Alcool achete (factures FCBS + Intermarche)</t>
         </is>
       </c>
-      <c r="C14" s="8" t="n">
+      <c r="C17" s="8" t="n">
         <v>10622</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>Factures fournisseurs</t>
         </is>
@@ -803,7 +872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -823,7 +892,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>La methode du fisc suppose doses exactes et zero perte : elle valorise comme CA verre des litres jamais vendus au verre. Valorisation au prix moyen liquide de 82 € / L (= CA reconstitue / litres reellement vendus au verre).</t>
+          <t>La methode du fisc suppose doses exactes et zero perte : elle valorise comme CA verre des litres jamais vendus au verre. Valorisation au prix moyen liquide de 78 € / L (= CA reconstitue / litres reellement vendus au verre).</t>
         </is>
       </c>
     </row>
@@ -872,7 +941,7 @@
         <v>5751</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>46427</v>
+        <v>44154</v>
       </c>
     </row>
     <row r="6">
@@ -893,7 +962,7 @@
         <v>2317</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>18702</v>
+        <v>17787</v>
       </c>
     </row>
     <row r="7">
@@ -914,7 +983,7 @@
         <v>1453</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>11730</v>
+        <v>11156</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +1004,7 @@
         <v>406</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>3281</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="9">
@@ -946,59 +1015,122 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Sur-versement au verre (~8 %)</t>
+          <t>Sur-versement au verre et cocktails (free-pour, Kerr 2008)</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>446</v>
+        <v>807</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>4532</v>
+        <v>8199</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>36584</v>
+        <v>62955</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t>Degustation</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Degustation offerte (pichet + vin nomme au verre)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>113</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1148</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>8815</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Cremant jete</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Cremant jete en fin de journee (eventé)</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>126</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>1280</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>9829</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Freinte biere</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Freinte technique de la biere pression (mousse, lignes)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>129</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1311</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>10063</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t>Perte reelle</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Perte reelle (casse, evaporation, fonds de verre, rincage)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
-        <v>2419</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>24578</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>198423</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="C13" s="5" t="n">
+        <v>1690</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>17171</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>131839</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Litres jamais vendus au verre, valorises a tort</t>
         </is>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="C14" s="8" t="n">
         <v>3842</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D14" s="8" t="n">
         <v>39036</v>
       </c>
-      <c r="E11" s="8" t="n">
-        <v>315146</v>
+      <c r="E14" s="8" t="n">
+        <v>299718</v>
       </c>
     </row>
   </sheetData>
@@ -1100,7 +1232,7 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>-315146</v>
+        <v>-299718</v>
       </c>
       <c r="C7" s="11" t="inlineStr"/>
       <c r="D7" s="12" t="inlineStr">
@@ -1116,10 +1248,10 @@
         </is>
       </c>
       <c r="B8" s="17" t="n">
-        <v>260107</v>
+        <v>275535</v>
       </c>
       <c r="C8" s="18" t="n">
-        <v>-175418</v>
+        <v>-159990</v>
       </c>
       <c r="D8" s="19" t="inlineStr">
         <is>
@@ -1130,7 +1262,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Perte reelle alcool : 2 419 L soit 22,8 % des achats - conforme a la norme CHR (15-25 %) et confirmee par le modele Monte Carlo (src/data/incertitudeDisparu).</t>
+          <t>Perte reelle alcool : 1 690 L soit 15,9 % des achats - conforme a la norme CHR (15-25 %) et confirmee par le modele Monte Carlo (src/data/incertitudeDisparu).</t>
         </is>
       </c>
     </row>

--- a/public/documents/pieces-defense/RF-reconstitution-volumes-liquides.xlsx
+++ b/public/documents/pieces-defense/RF-reconstitution-volumes-liquides.xlsx
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0.01063829787234043</v>
+        <v>0.01186217284880437</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>1690</v>
+        <v>1677</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0.1591037469403126</v>
+        <v>0.1578798719638486</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
@@ -1040,13 +1040,13 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>1148</v>
+        <v>1280</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>8815</v>
+        <v>9829</v>
       </c>
     </row>
     <row r="11">
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1690</v>
+        <v>1677</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>17171</v>
+        <v>17039</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>131839</v>
+        <v>130824</v>
       </c>
     </row>
     <row r="14">
@@ -1262,7 +1262,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Perte reelle alcool : 1 690 L soit 15,9 % des achats - conforme a la norme CHR (15-25 %) et confirmee par le modele Monte Carlo (src/data/incertitudeDisparu).</t>
+          <t>Perte reelle alcool : 1 677 L soit 15,8 % des achats - conforme a la norme CHR (15-25 %) et confirmee par le modele Monte Carlo (src/data/incertitudeDisparu).</t>
         </is>
       </c>
     </row>

--- a/public/documents/pieces-defense/RF-reconstitution-volumes-liquides.xlsx
+++ b/public/documents/pieces-defense/RF-reconstitution-volumes-liquides.xlsx
@@ -511,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -708,14 +708,14 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Sur-versement au verre et cocktails (free-pour, Kerr 2008)</t>
+          <t>Sur-versement vins/spiritueux/cocktails (free-pour : Kerr 2008, Wansink 2005)</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>807</v>
+        <v>1058</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0.07597439276972322</v>
+        <v>0.09960459423837319</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Degustation offerte (pichet + vin nomme au verre)</t>
+          <t>Degustation offerte (note par note, annexe C)</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>126</v>
+        <v>260</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0.01186217284880437</v>
+        <v>0.02447749952927886</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
@@ -772,19 +772,19 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Freinte biere</t>
+          <t>Cremant sur-verse</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Freinte technique de la biere pression (mousse, lignes)</t>
+          <t>Cremant sur-versé (free-pour +23,6 %)</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>129</v>
+        <v>87</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>0.01214460553568066</v>
+        <v>0.00819054791941254</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
@@ -795,67 +795,90 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Freinte biere</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Stock final (inventaire)</t>
+          <t>Freinte technique de la biere pression (mousse, lignes)</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>213</v>
+        <v>129</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.02005272076821691</v>
+        <v>0.01214460553568066</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Mesure (caisse/inventaire)</t>
+          <t>Estimation bornee</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Stock final (inventaire)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>213</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>0.02005272076821691</v>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Mesure (caisse/inventaire)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
           <t>Perte reelle</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Perte reelle (casse, evaporation, fonds de verre, rincage)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="n">
-        <v>1677</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>0.1578798719638486</v>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="C17" s="5" t="n">
+        <v>1205</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>0.1134437958953116</v>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Residu (= achats - traces)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>TOTAL ACHATS</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Alcool achete (factures FCBS + Intermarche)</t>
         </is>
       </c>
-      <c r="C17" s="8" t="n">
+      <c r="C18" s="8" t="n">
         <v>10622</v>
       </c>
-      <c r="D17" s="9" t="n">
+      <c r="D18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>Factures fournisseurs</t>
         </is>
@@ -872,7 +895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -892,7 +915,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>La methode du fisc suppose doses exactes et zero perte : elle valorise comme CA verre des litres jamais vendus au verre. Valorisation au prix moyen liquide de 78 € / L (= CA reconstitue / litres reellement vendus au verre).</t>
+          <t>La methode du fisc suppose doses exactes et zero perte : elle valorise comme CA verre des litres jamais vendus au verre. Valorisation au prix moyen liquide de 75 € / L (= CA reconstitue / litres reellement vendus au verre).</t>
         </is>
       </c>
     </row>
@@ -941,7 +964,7 @@
         <v>5751</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>44154</v>
+        <v>42701</v>
       </c>
     </row>
     <row r="6">
@@ -962,7 +985,7 @@
         <v>2317</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>17787</v>
+        <v>17201</v>
       </c>
     </row>
     <row r="7">
@@ -983,7 +1006,7 @@
         <v>1453</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>11156</v>
+        <v>10788</v>
       </c>
     </row>
     <row r="8">
@@ -1004,7 +1027,7 @@
         <v>406</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>3120</v>
+        <v>3018</v>
       </c>
     </row>
     <row r="9">
@@ -1015,17 +1038,17 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Sur-versement au verre et cocktails (free-pour, Kerr 2008)</t>
+          <t>Sur-versement vins/spiritueux/cocktails (free-pour : Kerr 2008, Wansink 2005)</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>807</v>
+        <v>1058</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>8199</v>
+        <v>10750</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>62955</v>
+        <v>79819</v>
       </c>
     </row>
     <row r="10">
@@ -1036,7 +1059,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Degustation offerte (pichet + vin nomme au verre)</t>
+          <t>Degustation offerte (note par note, annexe C)</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -1046,7 +1069,7 @@
         <v>1280</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>9829</v>
+        <v>9506</v>
       </c>
     </row>
     <row r="11">
@@ -1061,76 +1084,97 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>126</v>
+        <v>260</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1280</v>
+        <v>2642</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>9829</v>
+        <v>19615</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Freinte biere</t>
+          <t>Cremant sur-verse</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Freinte technique de la biere pression (mousse, lignes)</t>
+          <t>Cremant sur-versé (free-pour +23,6 %)</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>129</v>
+        <v>87</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>1311</v>
+        <v>884</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>10063</v>
+        <v>6564</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t>Freinte biere</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Freinte technique de la biere pression (mousse, lignes)</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>129</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1311</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>9732</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t>Perte reelle</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Perte reelle (casse, evaporation, fonds de verre, rincage)</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n">
-        <v>1677</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>17039</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>130824</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="C14" s="5" t="n">
+        <v>1205</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>12243</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>90909</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Litres jamais vendus au verre, valorises a tort</t>
         </is>
       </c>
-      <c r="C14" s="8" t="n">
+      <c r="C15" s="8" t="n">
         <v>3842</v>
       </c>
-      <c r="D14" s="8" t="n">
+      <c r="D15" s="8" t="n">
         <v>39036</v>
       </c>
-      <c r="E14" s="8" t="n">
-        <v>299718</v>
+      <c r="E15" s="8" t="n">
+        <v>289852</v>
       </c>
     </row>
   </sheetData>
@@ -1232,7 +1276,7 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>-299718</v>
+        <v>-289852</v>
       </c>
       <c r="C7" s="11" t="inlineStr"/>
       <c r="D7" s="12" t="inlineStr">
@@ -1248,10 +1292,10 @@
         </is>
       </c>
       <c r="B8" s="17" t="n">
-        <v>275535</v>
+        <v>285401</v>
       </c>
       <c r="C8" s="18" t="n">
-        <v>-159990</v>
+        <v>-150124</v>
       </c>
       <c r="D8" s="19" t="inlineStr">
         <is>
@@ -1262,7 +1306,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Perte reelle alcool : 1 677 L soit 15,8 % des achats - conforme a la norme CHR (15-25 %) et confirmee par le modele Monte Carlo (src/data/incertitudeDisparu).</t>
+          <t>Perte reelle alcool : 1 205 L soit 11,3 % des achats - conforme a la norme CHR (15-25 %) et confirmee par le modele Monte Carlo (src/data/incertitudeDisparu).</t>
         </is>
       </c>
     </row>

--- a/public/documents/pieces-defense/RF-reconstitution-volumes-liquides.xlsx
+++ b/public/documents/pieces-defense/RF-reconstitution-volumes-liquides.xlsx
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1058</v>
+        <v>720</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0.09960459423837319</v>
+        <v>0.06778384485031068</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1205</v>
+        <v>1543</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0.1134437958953116</v>
+        <v>0.1452645452833741</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Alcool achete (factures FCBS + Intermarche)</t>
+          <t>Alcool achete (factures fournisseurs)</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
@@ -915,7 +915,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>La methode du fisc suppose doses exactes et zero perte : elle valorise comme CA verre des litres jamais vendus au verre. Valorisation au prix moyen liquide de 75 € / L (= CA reconstitue / litres reellement vendus au verre).</t>
+          <t>La methode du fisc suppose doses exactes et zero perte : elle valorise comme CA verre des litres jamais vendus au verre. Valorisation au prix moyen liquide de 79 € / L (= CA reconstitue / litres reellement vendus au verre).</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
         <v>5751</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>42701</v>
+        <v>44681</v>
       </c>
     </row>
     <row r="6">
@@ -985,7 +985,7 @@
         <v>2317</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>17201</v>
+        <v>17999</v>
       </c>
     </row>
     <row r="7">
@@ -1006,7 +1006,7 @@
         <v>1453</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>10788</v>
+        <v>11289</v>
       </c>
     </row>
     <row r="8">
@@ -1027,7 +1027,7 @@
         <v>406</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>3018</v>
+        <v>3158</v>
       </c>
     </row>
     <row r="9">
@@ -1042,13 +1042,13 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1058</v>
+        <v>720</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>10750</v>
+        <v>7316</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>79819</v>
+        <v>56839</v>
       </c>
     </row>
     <row r="10">
@@ -1069,7 +1069,7 @@
         <v>1280</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>9506</v>
+        <v>9947</v>
       </c>
     </row>
     <row r="11">
@@ -1090,7 +1090,7 @@
         <v>2642</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>19615</v>
+        <v>20525</v>
       </c>
     </row>
     <row r="12">
@@ -1111,7 +1111,7 @@
         <v>884</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>6564</v>
+        <v>6868</v>
       </c>
     </row>
     <row r="13">
@@ -1132,7 +1132,7 @@
         <v>1311</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>9732</v>
+        <v>10184</v>
       </c>
     </row>
     <row r="14">
@@ -1147,13 +1147,13 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>1205</v>
+        <v>1543</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>12243</v>
+        <v>15678</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>90909</v>
+        <v>121808</v>
       </c>
     </row>
     <row r="15">
@@ -1174,7 +1174,7 @@
         <v>39036</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>289852</v>
+        <v>303297</v>
       </c>
     </row>
   </sheetData>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>-289852</v>
+        <v>-303297</v>
       </c>
       <c r="C7" s="11" t="inlineStr"/>
       <c r="D7" s="12" t="inlineStr">
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="B8" s="17" t="n">
-        <v>285401</v>
+        <v>271956</v>
       </c>
       <c r="C8" s="18" t="n">
-        <v>-150124</v>
+        <v>-163569</v>
       </c>
       <c r="D8" s="19" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Perte reelle alcool : 1 205 L soit 11,3 % des achats - conforme a la norme CHR (15-25 %) et confirmee par le modele Monte Carlo (src/data/incertitudeDisparu).</t>
+          <t>Perte reelle alcool : 1 543 L soit 14,5 % des achats - conforme a la norme CHR (15-25 %) et confirmee par le modele Monte Carlo (src/data/incertitudeDisparu).</t>
         </is>
       </c>
     </row>
